--- a/dummy-files/test-charges-5x-and-999.xlsx
+++ b/dummy-files/test-charges-5x-and-999.xlsx
@@ -426,7 +426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-01T12:26:19.653458</t>
+          <t>Generated: 2026-05-19T18:51:22.745912</t>
         </is>
       </c>
     </row>

--- a/dummy-files/test-charges-5x-and-999.xlsx
+++ b/dummy-files/test-charges-5x-and-999.xlsx
@@ -426,7 +426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-19T18:51:22.745912</t>
+          <t>Generated: 2026-05-27T21:09:21.835298</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>

--- a/dummy-files/test-charges-5x-and-999.xlsx
+++ b/dummy-files/test-charges-5x-and-999.xlsx
@@ -426,7 +426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-27T21:09:21.835298</t>
+          <t>Generated: 2026-06-25T20:30:37.822128</t>
         </is>
       </c>
     </row>
